--- a/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_audio.xlsx
+++ b/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_audio.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="11775"/>
   </bookViews>
   <sheets>
     <sheet name="cfg_audio" sheetId="1" r:id="rId1"/>
@@ -3851,7 +3851,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:8">
       <c r="A21" t="s">
         <v>79</v>
       </c>
@@ -3874,7 +3874,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:8">
       <c r="A22" t="s">
         <v>82</v>
       </c>
@@ -3897,7 +3897,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:8">
       <c r="A23" t="s">
         <v>85</v>
       </c>
@@ -3920,7 +3920,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:8">
       <c r="A24" t="s">
         <v>90</v>
       </c>
@@ -3943,7 +3943,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:8">
       <c r="A25" t="s">
         <v>93</v>
       </c>
@@ -3966,7 +3966,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:8">
       <c r="A26" t="s">
         <v>96</v>
       </c>
@@ -3989,7 +3989,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:8">
       <c r="A27" t="s">
         <v>100</v>
       </c>
@@ -4012,7 +4012,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:8">
       <c r="A28" t="s">
         <v>103</v>
       </c>
@@ -4035,7 +4035,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:8">
       <c r="A29" t="s">
         <v>106</v>
       </c>
@@ -4058,7 +4058,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:8">
       <c r="A30" t="s">
         <v>109</v>
       </c>
@@ -4081,7 +4081,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:8">
       <c r="A31" t="s">
         <v>112</v>
       </c>
@@ -4104,7 +4104,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:8">
       <c r="A32" t="s">
         <v>115</v>
       </c>
